--- a/data/sens_input.xlsx
+++ b/data/sens_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Google Drive\PycharmProjects\prg-opf\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D80741-5656-4724-8AA1-1592ED749E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBF4091-A5D2-4688-936D-AE04810C6284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52800" yWindow="5400" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ports" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -472,7 +472,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>-18</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -486,7 +486,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-16</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -500,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>-14</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-10</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -542,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -556,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>-4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -584,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -612,7 +612,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -640,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -668,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -710,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -724,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -738,7 +738,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/sens_input.xlsx
+++ b/data/sens_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Google Drive\PycharmProjects\prg-opf\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBF4091-A5D2-4688-936D-AE04810C6284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0324D2E-1E2A-46C2-97BB-330B1129CBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52800" yWindow="5400" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ports" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -486,7 +486,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -500,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -542,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -556,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -584,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -612,7 +612,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -640,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -668,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>0.6</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -710,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -724,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -738,7 +738,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
